--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEF6930-5247-46FE-A6AF-C9E35DD47C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515F548B-43F7-4C5F-9BEC-AB4E3E040E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="85">
-  <si>
-    <t>م</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>اسم المشروع</t>
   </si>
@@ -135,42 +132,27 @@
     <t>26200</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 2.6M)</t>
-  </si>
-  <si>
     <t>تم السداد بالكامل</t>
   </si>
   <si>
     <t>26100</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 4.4M)</t>
-  </si>
-  <si>
     <t>جاري السداد</t>
   </si>
   <si>
     <t>26300</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 3.5M)</t>
-  </si>
-  <si>
     <t>غير مدفوع</t>
   </si>
   <si>
     <t>26400</t>
   </si>
   <si>
-    <t>شركة أملاك العالمية (تمويل 2.2M)</t>
-  </si>
-  <si>
     <t>إجمالي التسهيلات (Total Loans)</t>
   </si>
   <si>
-    <t>رقم القسط</t>
-  </si>
-  <si>
     <t>بيان الدفعة</t>
   </si>
   <si>
@@ -195,81 +177,45 @@
     <t>حالة القسط</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 2.6M - قسط كامل)</t>
-  </si>
-  <si>
     <t>2026-05-23</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 4.4M - قسط كامل)</t>
-  </si>
-  <si>
     <t>2026-07-26</t>
   </si>
   <si>
     <t>سداد جزئي (متبقي 4.46M)</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 3.5M - دفعة 1)</t>
-  </si>
-  <si>
     <t>2027-04-01</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 3.5M - دفعة 2)</t>
-  </si>
-  <si>
     <t>2027-04-14</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 3.5M - دفعة 3)</t>
-  </si>
-  <si>
     <t>2027-05-11</t>
   </si>
   <si>
-    <t>منصة دينار (صكوك 3.5M - دفعة 4)</t>
-  </si>
-  <si>
     <t>2027-06-01</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 1)</t>
-  </si>
-  <si>
     <t>2026-08-02</t>
   </si>
   <si>
     <t>تم السداد</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 2)</t>
-  </si>
-  <si>
     <t>2027-02-02</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 3)</t>
-  </si>
-  <si>
     <t>2027-08-02</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 4)</t>
-  </si>
-  <si>
     <t>2028-02-02</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 5)</t>
-  </si>
-  <si>
     <t>2028-08-02</t>
   </si>
   <si>
-    <t>أملاك العالمية (قسط 6)</t>
-  </si>
-  <si>
     <t>2029-02-02</t>
   </si>
   <si>
@@ -280,6 +226,54 @@
   </si>
   <si>
     <t>المبلغ</t>
+  </si>
+  <si>
+    <t>دينار (2.6M)</t>
+  </si>
+  <si>
+    <t>دينار (4.4M)</t>
+  </si>
+  <si>
+    <t>دينار (3.5M)</t>
+  </si>
+  <si>
+    <t>أملاك  (2.2M)</t>
+  </si>
+  <si>
+    <t>دينار (2.6M - قسط كامل)</t>
+  </si>
+  <si>
+    <t>دينار (4.4M - قسط كامل)</t>
+  </si>
+  <si>
+    <t>دينار (3.5M - دفعة 1)</t>
+  </si>
+  <si>
+    <t>دينار (3.5M - دفعة 2)</t>
+  </si>
+  <si>
+    <t>دينار (3.5M - دفعة 3)</t>
+  </si>
+  <si>
+    <t>دينار (3.5M - دفعة 4)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 1)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 2)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 3)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 4)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 5)</t>
+  </si>
+  <si>
+    <t>أملاك (2.2M دفعة 6)</t>
   </si>
 </sst>
 </file>
@@ -360,7 +354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -439,30 +433,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF1F4E78"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -484,17 +454,6 @@
       <bottom style="medium">
         <color rgb="FF1F4E78"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -556,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -573,10 +532,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -632,25 +587,16 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -659,7 +605,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -668,30 +614,479 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
+  <dxfs count="55">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF1F4E78"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9D9D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFD9D9D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1067,7 +1462,9 @@
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFD9D9D9"/>
+        </right>
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
@@ -1131,8 +1528,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
@@ -1172,74 +1568,6 @@
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
@@ -1388,39 +1716,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FFD9D9D9"/>
@@ -1809,475 +2104,6 @@
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF1F4E78"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
         <right style="thin">
           <color rgb="FFD9D9D9"/>
         </right>
@@ -2335,82 +2161,78 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:K7" totalsRowShown="0" headerRowDxfId="44" dataDxfId="45" headerRowBorderDxfId="57" tableBorderDxfId="58" totalsRowBorderDxfId="56">
-  <autoFilter ref="B3:K7" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1E1F22D1-015B-49C7-B0E9-F407693D8DAB}" name="م" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="51">
-      <calculatedColumnFormula>IF(E4&gt;0, (G4-E4)/E4, 0)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:J7" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+  <autoFilter ref="B3:J7" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}"/>
+  <tableColumns count="9">
+    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="6">
+      <calculatedColumnFormula>IF(D4&gt;0, (F4-D4)/D4, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="50">
-      <calculatedColumnFormula>SUMIF($C$12:$C$23, C4, $G$12:$G$23)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="5">
+      <calculatedColumnFormula>SUMIF($B$12:$B$23, B4, $F$12:$F$23)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="49">
-      <calculatedColumnFormula>SUMIF($C$12:$C$23, C4, $H$12:$H$23)</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="4">
+      <calculatedColumnFormula>SUMIF($B$12:$B$23, B4, $G$12:$G$23)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="48">
-      <calculatedColumnFormula>G4-H4</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="3">
+      <calculatedColumnFormula>F4-G4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1078F62B-3C12-467A-8037-C551AFC45BAE}" name="نسبة السداد %" dataDxfId="47">
-      <calculatedColumnFormula>IF(G4&gt;0, H4/G4, 0)</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{1078F62B-3C12-467A-8037-C551AFC45BAE}" name="نسبة السداد %" dataDxfId="2">
+      <calculatedColumnFormula>IF(F4&gt;0, G4/F4, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8CB32CEA-EA37-4F1D-9E25-9783A00F1897}" name="حالة القرض" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{8CB32CEA-EA37-4F1D-9E25-9783A00F1897}" name="حالة القرض" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B11:K23" totalsRowShown="0" headerRowDxfId="29" dataDxfId="30" headerRowBorderDxfId="42" tableBorderDxfId="43" totalsRowBorderDxfId="41">
-  <autoFilter ref="B11:K23" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A37AB871-20AA-49BD-A888-9AF1A2092FE9}" name="رقم القسط" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="36">
-      <calculatedColumnFormula>IF(I12&gt;0,E12-TODAY(),"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B11:J23" totalsRowShown="0" headerRowDxfId="41" dataDxfId="42" headerRowBorderDxfId="53" tableBorderDxfId="54" totalsRowBorderDxfId="52">
+  <autoFilter ref="B11:J23" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}"/>
+  <tableColumns count="9">
+    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="48">
+      <calculatedColumnFormula>IF(H12&gt;0,D12-TODAY(),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="33">
-      <calculatedColumnFormula>G12-H12</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="45">
+      <calculatedColumnFormula>F12-G12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="32">
-      <calculatedColumnFormula>J11+H12</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="44">
+      <calculatedColumnFormula>I11+G12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A08612B9-95BC-4628-A43C-26F0A8B3B756}" name="حالة القسط" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{A08612B9-95BC-4628-A43C-26F0A8B3B756}" name="حالة القسط" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B30:D34" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
-  <autoFilter ref="B30:D34" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EC8C4173-E0A5-405D-993A-50D9F7BF5516}" name="م" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B30:C35" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
+  <autoFilter ref="B30:C35" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}"/>
+  <tableColumns count="2">
+    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B38:G42" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="20" tableBorderDxfId="21" totalsRowBorderDxfId="19">
-  <autoFilter ref="B38:G42" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{B44F3029-FA59-4685-B96B-62DE29084609}" name="م" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{7BB8F3DA-2FCB-4C6E-979A-002269AD8AD1}" name="إجمالي التكلفة" dataDxfId="13">
-      <calculatedColumnFormula>E39+F39</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B38:F43" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
+  <autoFilter ref="B38:F43" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}"/>
+  <tableColumns count="5">
+    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{7BB8F3DA-2FCB-4C6E-979A-002269AD8AD1}" name="إجمالي التكلفة" dataDxfId="0">
+      <calculatedColumnFormula>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2418,27 +2240,27 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B47:C49" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B47:C49" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="26">
   <autoFilter ref="B47:C49" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B54:F55" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B54:F55" totalsRowShown="0" headerRowDxfId="15" dataDxfId="16" tableBorderDxfId="22">
   <autoFilter ref="B54:F55" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="18">
       <calculatedColumnFormula>IF(C55&gt;0, D55/C55, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2733,1015 +2555,924 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" customWidth="1"/>
     <col min="4" max="4" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="10" width="13.88671875" customWidth="1"/>
+    <col min="7" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="14">
+        <v>2600000</v>
+      </c>
+      <c r="E4" s="15">
+        <f>IF(D4&gt;0, (F4-D4)/D4, 0)</f>
+        <v>0.14560000000000001</v>
+      </c>
+      <c r="F4" s="14">
+        <f>SUMIF($B$12:$B$23, B4, $F$12:$F$23)</f>
+        <v>2978560</v>
+      </c>
+      <c r="G4" s="14">
+        <f>SUMIF($B$12:$B$23, B4, $G$12:$G$23)</f>
+        <v>2978560</v>
+      </c>
+      <c r="H4" s="14">
+        <f>F4-G4</f>
         <v>0</v>
       </c>
-      <c r="C3" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="27">
+      <c r="I4" s="15">
+        <f>IF(F4&gt;0, G4/F4, 0)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="J4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="16">
-        <v>2600000</v>
-      </c>
-      <c r="F4" s="17">
-        <f>IF(E4&gt;0, (G4-E4)/E4, 0)</f>
-        <v>0.14560000000000001</v>
-      </c>
-      <c r="G4" s="16">
-        <f>SUMIF($C$12:$C$23, C4, $G$12:$G$23)</f>
-        <v>2978560</v>
-      </c>
-      <c r="H4" s="16">
-        <f>SUMIF($C$12:$C$23, C4, $H$12:$H$23)</f>
-        <v>2978560</v>
-      </c>
-      <c r="I4" s="16">
-        <f>G4-H4</f>
+      <c r="C5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="14">
+        <v>4400000</v>
+      </c>
+      <c r="E5" s="15">
+        <f>IF(D5&gt;0, (F5-D5)/D5, 0)</f>
+        <v>0.18293000000000001</v>
+      </c>
+      <c r="F5" s="14">
+        <f>SUMIF($B$12:$B$23, B5, $F$12:$F$23)</f>
+        <v>5204892</v>
+      </c>
+      <c r="G5" s="14">
+        <f>SUMIF($B$12:$B$23, B5, $G$12:$G$23)</f>
+        <v>740440</v>
+      </c>
+      <c r="H5" s="14">
+        <f>F5-G5</f>
+        <v>4464452</v>
+      </c>
+      <c r="I5" s="15">
+        <f>IF(F5&gt;0, G5/F5, 0)</f>
+        <v>0.14225847529593313</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="14">
+        <v>3500000</v>
+      </c>
+      <c r="E6" s="15">
+        <f>IF(D6&gt;0, (F6-D6)/D6, 0)</f>
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="F6" s="14">
+        <f>SUMIF($B$12:$B$23, B6, $F$12:$F$23)</f>
+        <v>4237100</v>
+      </c>
+      <c r="G6" s="14">
+        <f>SUMIF($B$12:$B$23, B6, $G$12:$G$23)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="17">
-        <f>IF(G4&gt;0, H4/G4, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="K4" s="28" t="s">
+      <c r="H6" s="14">
+        <f>F6-G6</f>
+        <v>4237100</v>
+      </c>
+      <c r="I6" s="15">
+        <f>IF(F6&gt;0, G6/F6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="23">
+        <v>2200000</v>
+      </c>
+      <c r="E7" s="24">
+        <f>IF(D7&gt;0, (F7-D7)/D7, 0)</f>
+        <v>0.315</v>
+      </c>
+      <c r="F7" s="23">
+        <f>SUMIF($B$12:$B$23, B7, $F$12:$F$23)</f>
+        <v>2893000</v>
+      </c>
+      <c r="G7" s="23">
+        <f>SUMIF($B$12:$B$23, B7, $G$12:$G$23)</f>
+        <v>115500</v>
+      </c>
+      <c r="H7" s="23">
+        <f>F7-G7</f>
+        <v>2777500</v>
+      </c>
+      <c r="I7" s="24">
+        <f>IF(F7&gt;0, G7/F7, 0)</f>
+        <v>3.9923954372623575E-2</v>
+      </c>
+      <c r="J7" s="28" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="27">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="16">
-        <v>4400000</v>
-      </c>
-      <c r="F5" s="17">
-        <f>IF(E5&gt;0, (G5-E5)/E5, 0)</f>
-        <v>0.18293000000000001</v>
-      </c>
-      <c r="G5" s="16">
-        <f>SUMIF($C$12:$C$23, C5, $G$12:$G$23)</f>
-        <v>5204892</v>
-      </c>
-      <c r="H5" s="16">
-        <f>SUMIF($C$12:$C$23, C5, $H$12:$H$23)</f>
-        <v>740440</v>
-      </c>
-      <c r="I5" s="16">
-        <f>G5-H5</f>
-        <v>4464452</v>
-      </c>
-      <c r="J5" s="17">
-        <f>IF(G5&gt;0, H5/G5, 0)</f>
-        <v>0.14225847529593313</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="27">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="16">
-        <v>3500000</v>
-      </c>
-      <c r="F6" s="17">
-        <f>IF(E6&gt;0, (G6-E6)/E6, 0)</f>
-        <v>0.21060000000000001</v>
-      </c>
-      <c r="G6" s="16">
-        <f>SUMIF($C$12:$C$23, C6, $G$12:$G$23)</f>
-        <v>4237100</v>
-      </c>
-      <c r="H6" s="16">
-        <f>SUMIF($C$12:$C$23, C6, $H$12:$H$23)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="16">
-        <f>G6-H6</f>
-        <v>4237100</v>
-      </c>
-      <c r="J6" s="17">
-        <f>IF(G6&gt;0, H6/G6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="32">
-        <v>4</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="25">
-        <v>2200000</v>
-      </c>
-      <c r="F7" s="26">
-        <f>IF(E7&gt;0, (G7-E7)/E7, 0)</f>
-        <v>0.315</v>
-      </c>
-      <c r="G7" s="25">
-        <f>SUMIF($C$12:$C$23, C7, $G$12:$G$23)</f>
-        <v>2893000</v>
-      </c>
-      <c r="H7" s="25">
-        <f>SUMIF($C$12:$C$23, C7, $H$12:$H$23)</f>
-        <v>115500</v>
-      </c>
-      <c r="I7" s="25">
-        <f>G7-H7</f>
-        <v>2777500</v>
-      </c>
-      <c r="J7" s="26">
-        <f>IF(G7&gt;0, H7/G7, 0)</f>
-        <v>3.9923954372623575E-2</v>
-      </c>
-      <c r="K7" s="33" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="16">
+        <f>SUM(D4:D7)</f>
+        <v>12700000</v>
+      </c>
+      <c r="E8" s="17">
+        <f>IF(D8&gt;0, (F8-D8)/D8, 0)</f>
+        <v>0.20579149606299213</v>
+      </c>
+      <c r="F8" s="16">
+        <f>SUM(F4:F7)</f>
+        <v>15313552</v>
+      </c>
+      <c r="G8" s="16">
+        <f>SUM(G4:G7)</f>
+        <v>3834500</v>
+      </c>
+      <c r="H8" s="16">
+        <f>SUM(H4:H7)</f>
+        <v>11479052</v>
+      </c>
+      <c r="I8" s="17">
+        <f>IF(F8&gt;0, G8/F8, 0)</f>
+        <v>0.25039912359980232</v>
+      </c>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+    </row>
+    <row r="11" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="18">
-        <f>SUM(E4:E7)</f>
-        <v>12700000</v>
-      </c>
-      <c r="F8" s="19">
-        <f>IF(E8&gt;0, (G8-E8)/E8, 0)</f>
-        <v>0.20579149606299213</v>
-      </c>
-      <c r="G8" s="18">
-        <f>SUM(G4:G7)</f>
+      <c r="H11" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="20" t="str">
+        <f ca="1">IF(H12&gt;0,D12-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="14">
+        <v>2978560</v>
+      </c>
+      <c r="G12" s="14">
+        <v>2978560</v>
+      </c>
+      <c r="H12" s="14">
+        <f>F12-G12</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="14">
+        <f>G12</f>
+        <v>2978560</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="20">
+        <f ca="1">IF(H13&gt;0,D13-TODAY(),"")</f>
+        <v>-23</v>
+      </c>
+      <c r="F13" s="14">
+        <v>5204892</v>
+      </c>
+      <c r="G13" s="14">
+        <v>740440</v>
+      </c>
+      <c r="H13" s="14">
+        <f>F13-G13</f>
+        <v>4464452</v>
+      </c>
+      <c r="I13" s="14">
+        <f>I12+G13</f>
+        <v>3719000</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="20">
+        <f ca="1">IF(H14&gt;0,D14-TODAY(),"")</f>
+        <v>226</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1210600</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <f>F14-G14</f>
+        <v>1210600</v>
+      </c>
+      <c r="I14" s="14">
+        <f>I13+G14</f>
+        <v>3719000</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="20">
+        <f ca="1">IF(H15&gt;0,D15-TODAY(),"")</f>
+        <v>239</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1210600</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <f>F15-G15</f>
+        <v>1210600</v>
+      </c>
+      <c r="I15" s="14">
+        <f>I14+G15</f>
+        <v>3719000</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="20">
+        <f ca="1">IF(H16&gt;0,D16-TODAY(),"")</f>
+        <v>266</v>
+      </c>
+      <c r="F16" s="14">
+        <v>1210600</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <f>F16-G16</f>
+        <v>1210600</v>
+      </c>
+      <c r="I16" s="14">
+        <f>I15+G16</f>
+        <v>3719000</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="20">
+        <f ca="1">IF(H17&gt;0,D17-TODAY(),"")</f>
+        <v>287</v>
+      </c>
+      <c r="F17" s="14">
+        <v>605300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <f>F17-G17</f>
+        <v>605300</v>
+      </c>
+      <c r="I17" s="14">
+        <f>I16+G17</f>
+        <v>3719000</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="20" t="str">
+        <f ca="1">IF(H18&gt;0,D18-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <v>115500</v>
+      </c>
+      <c r="G18" s="14">
+        <v>115500</v>
+      </c>
+      <c r="H18" s="14">
+        <f>F18-G18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="14">
+        <f>I17+G18</f>
+        <v>3834500</v>
+      </c>
+      <c r="J18" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="20">
+        <f ca="1">IF(H19&gt;0,D19-TODAY(),"")</f>
+        <v>168</v>
+      </c>
+      <c r="F19" s="14">
+        <v>115500</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <f>F19-G19</f>
+        <v>115500</v>
+      </c>
+      <c r="I19" s="14">
+        <f>I18+G19</f>
+        <v>3834500</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="20">
+        <f ca="1">IF(H20&gt;0,D20-TODAY(),"")</f>
+        <v>349</v>
+      </c>
+      <c r="F20" s="14">
+        <v>115500</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <f>F20-G20</f>
+        <v>115500</v>
+      </c>
+      <c r="I20" s="14">
+        <f>I19+G20</f>
+        <v>3834500</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="20">
+        <f ca="1">IF(H21&gt;0,D21-TODAY(),"")</f>
+        <v>533</v>
+      </c>
+      <c r="F21" s="14">
+        <v>115500</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <f>F21-G21</f>
+        <v>115500</v>
+      </c>
+      <c r="I21" s="14">
+        <f>I20+G21</f>
+        <v>3834500</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="20">
+        <f ca="1">IF(H22&gt;0,D22-TODAY(),"")</f>
+        <v>715</v>
+      </c>
+      <c r="F22" s="14">
+        <v>115500</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <f>F22-G22</f>
+        <v>115500</v>
+      </c>
+      <c r="I22" s="14">
+        <f>I21+G22</f>
+        <v>3834500</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="29">
+        <f ca="1">IF(H23&gt;0,D23-TODAY(),"")</f>
+        <v>899</v>
+      </c>
+      <c r="F23" s="23">
+        <v>2315500</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23">
+        <f>F23-G23</f>
+        <v>2315500</v>
+      </c>
+      <c r="I23" s="23">
+        <f>I22+G23</f>
+        <v>3834500</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="16">
+        <f>SUM(F12:F23)</f>
         <v>15313552</v>
       </c>
-      <c r="H8" s="18">
-        <f>SUM(H4:H7)</f>
+      <c r="G24" s="16">
+        <f>SUM(G12:G23)</f>
         <v>3834500</v>
       </c>
-      <c r="I8" s="18">
-        <f>SUM(I4:I7)</f>
+      <c r="H24" s="16">
+        <f>SUM(H12:H23)</f>
         <v>11479052</v>
       </c>
-      <c r="J8" s="19">
-        <f>IF(G8&gt;0, H8/G8, 0)</f>
-        <v>0.25039912359980232</v>
-      </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-    </row>
-    <row r="11" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="27">
+      <c r="I24" s="16">
+        <f>I23</f>
+        <v>3834500</v>
+      </c>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="30">
+        <v>1810000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="30">
+        <v>1925000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="30">
+        <v>4070000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="31">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="43">
+        <f>SUBTOTAL(109,C31:C34)</f>
+        <v>7855000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="22" t="str">
-        <f ca="1">IF(I12&gt;0,E12-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="16">
-        <v>2978560</v>
-      </c>
-      <c r="H12" s="16">
-        <v>2978560</v>
-      </c>
-      <c r="I12" s="16">
-        <f>G12-H12</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="16">
-        <f>H12</f>
-        <v>2978560</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="27">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="22">
-        <f ca="1">IF(I13&gt;0,E13-TODAY(),"")</f>
-        <v>-22</v>
-      </c>
-      <c r="G13" s="16">
-        <v>5204892</v>
-      </c>
-      <c r="H13" s="16">
-        <v>740440</v>
-      </c>
-      <c r="I13" s="16">
-        <f>G13-H13</f>
-        <v>4464452</v>
-      </c>
-      <c r="J13" s="16">
-        <f>J12+H13</f>
-        <v>3719000</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="27">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="22">
-        <f ca="1">IF(I14&gt;0,E14-TODAY(),"")</f>
-        <v>227</v>
-      </c>
-      <c r="G14" s="16">
-        <v>1210600</v>
-      </c>
-      <c r="H14" s="16">
-        <v>0</v>
-      </c>
-      <c r="I14" s="16">
-        <f>G14-H14</f>
-        <v>1210600</v>
-      </c>
-      <c r="J14" s="16">
-        <f>J13+H14</f>
-        <v>3719000</v>
-      </c>
-      <c r="K14" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="27">
-        <v>4</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="22">
-        <f ca="1">IF(I15&gt;0,E15-TODAY(),"")</f>
-        <v>240</v>
-      </c>
-      <c r="G15" s="16">
-        <v>1210600</v>
-      </c>
-      <c r="H15" s="16">
-        <v>0</v>
-      </c>
-      <c r="I15" s="16">
-        <f>G15-H15</f>
-        <v>1210600</v>
-      </c>
-      <c r="J15" s="16">
-        <f>J14+H15</f>
-        <v>3719000</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="27">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="22">
-        <f ca="1">IF(I16&gt;0,E16-TODAY(),"")</f>
-        <v>267</v>
-      </c>
-      <c r="G16" s="16">
-        <v>1210600</v>
-      </c>
-      <c r="H16" s="16">
-        <v>0</v>
-      </c>
-      <c r="I16" s="16">
-        <f>G16-H16</f>
-        <v>1210600</v>
-      </c>
-      <c r="J16" s="16">
-        <f>J15+H16</f>
-        <v>3719000</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="27">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="22">
-        <f ca="1">IF(I17&gt;0,E17-TODAY(),"")</f>
-        <v>288</v>
-      </c>
-      <c r="G17" s="16">
-        <v>605300</v>
-      </c>
-      <c r="H17" s="16">
-        <v>0</v>
-      </c>
-      <c r="I17" s="16">
-        <f>G17-H17</f>
-        <v>605300</v>
-      </c>
-      <c r="J17" s="16">
-        <f>J16+H17</f>
-        <v>3719000</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="27">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="22" t="str">
-        <f ca="1">IF(I18&gt;0,E18-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <v>115500</v>
-      </c>
-      <c r="H18" s="16">
-        <v>115500</v>
-      </c>
-      <c r="I18" s="16">
-        <f>G18-H18</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="16">
-        <f>J17+H18</f>
-        <v>3834500</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="27">
+      <c r="E38" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="22">
-        <f ca="1">IF(I19&gt;0,E19-TODAY(),"")</f>
-        <v>169</v>
-      </c>
-      <c r="G19" s="16">
-        <v>115500</v>
-      </c>
-      <c r="H19" s="16">
-        <v>0</v>
-      </c>
-      <c r="I19" s="16">
-        <f>G19-H19</f>
-        <v>115500</v>
-      </c>
-      <c r="J19" s="16">
-        <f>J18+H19</f>
-        <v>3834500</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="27">
+      <c r="F38" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="22">
-        <f ca="1">IF(I20&gt;0,E20-TODAY(),"")</f>
-        <v>350</v>
-      </c>
-      <c r="G20" s="16">
-        <v>115500</v>
-      </c>
-      <c r="H20" s="16">
-        <v>0</v>
-      </c>
-      <c r="I20" s="16">
-        <f>G20-H20</f>
-        <v>115500</v>
-      </c>
-      <c r="J20" s="16">
-        <f>J19+H20</f>
-        <v>3834500</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="27">
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="22">
-        <f ca="1">IF(I21&gt;0,E21-TODAY(),"")</f>
-        <v>534</v>
-      </c>
-      <c r="G21" s="16">
-        <v>115500</v>
-      </c>
-      <c r="H21" s="16">
-        <v>0</v>
-      </c>
-      <c r="I21" s="16">
-        <f>G21-H21</f>
-        <v>115500</v>
-      </c>
-      <c r="J21" s="16">
-        <f>J20+H21</f>
-        <v>3834500</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="27">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" s="22">
-        <f ca="1">IF(I22&gt;0,E22-TODAY(),"")</f>
-        <v>716</v>
-      </c>
-      <c r="G22" s="16">
-        <v>115500</v>
-      </c>
-      <c r="H22" s="16">
-        <v>0</v>
-      </c>
-      <c r="I22" s="16">
-        <f>G22-H22</f>
-        <v>115500</v>
-      </c>
-      <c r="J22" s="16">
-        <f>J21+H22</f>
-        <v>3834500</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="32">
-        <v>12</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="34">
-        <f ca="1">IF(I23&gt;0,E23-TODAY(),"")</f>
-        <v>900</v>
-      </c>
-      <c r="G23" s="25">
-        <v>2315500</v>
-      </c>
-      <c r="H23" s="25">
-        <v>0</v>
-      </c>
-      <c r="I23" s="25">
-        <f>G23-H23</f>
-        <v>2315500</v>
-      </c>
-      <c r="J23" s="25">
-        <f>J22+H23</f>
-        <v>3834500</v>
-      </c>
-      <c r="K23" s="33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="18">
-        <f>SUM(G12:G23)</f>
-        <v>15313552</v>
-      </c>
-      <c r="H24" s="18">
-        <f>SUM(H12:H23)</f>
-        <v>3834500</v>
-      </c>
-      <c r="I24" s="18">
-        <f>SUM(I12:I23)</f>
-        <v>11479052</v>
-      </c>
-      <c r="J24" s="18">
-        <f>J23</f>
-        <v>3834500</v>
-      </c>
-      <c r="K24" s="10"/>
-    </row>
-    <row r="25" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="27">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="35">
-        <v>1810000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="27">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="35">
-        <v>1925000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="27">
-        <v>3</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="35">
-        <v>4070000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="32">
-        <v>4</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="36">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7">
-        <f>SUM(D31:D34)</f>
-        <v>7855000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="27">
-        <v>1</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="4">
+        <v>5000000</v>
+      </c>
+      <c r="E39" s="4">
+        <v>13000000</v>
+      </c>
+      <c r="F39" s="30">
+        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="4">
-        <v>5000000</v>
-      </c>
-      <c r="F39" s="4">
-        <v>13000000</v>
-      </c>
-      <c r="G39" s="35">
-        <f>E39+F39</f>
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="27">
-        <v>2</v>
-      </c>
       <c r="C40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3500000</v>
+      </c>
+      <c r="E40" s="4">
+        <v>8000000</v>
+      </c>
+      <c r="F40" s="30">
+        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
+        <v>11500000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="4">
-        <v>3500000</v>
-      </c>
-      <c r="F40" s="4">
+      <c r="C41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="4">
         <v>8000000</v>
       </c>
-      <c r="G40" s="35">
-        <f>E40+F40</f>
-        <v>11500000</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="27">
-        <v>3</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="E41" s="4">
+        <v>27000000</v>
+      </c>
+      <c r="F41" s="30">
+        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="4">
-        <v>8000000</v>
-      </c>
-      <c r="F41" s="4">
-        <v>27000000</v>
-      </c>
-      <c r="G41" s="35">
-        <f>E41+F41</f>
-        <v>35000000</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="32">
-        <v>4</v>
-      </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="32">
+        <v>4200000</v>
+      </c>
+      <c r="E42" s="32">
+        <v>6800000</v>
+      </c>
+      <c r="F42" s="31">
+        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="42"/>
+      <c r="D43" s="44">
+        <f>SUBTOTAL(109,D39:D42)</f>
+        <v>20700000</v>
+      </c>
+      <c r="E43" s="44">
+        <f>SUBTOTAL(109,E39:E42)</f>
+        <v>54800000</v>
+      </c>
+      <c r="F43" s="43">
+        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
+        <v>75500000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="37">
-        <v>4200000</v>
-      </c>
-      <c r="F42" s="37">
-        <v>6800000</v>
-      </c>
-      <c r="G42" s="36">
-        <f>E42+F42</f>
-        <v>11000000</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="7">
-        <f>SUM(E39:E42)</f>
-        <v>20700000</v>
-      </c>
-      <c r="F43" s="7">
-        <f>SUM(F39:F42)</f>
-        <v>54800000</v>
-      </c>
-      <c r="G43" s="7">
-        <f>SUM(G39:G42)</f>
-        <v>75500000</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="38" t="s">
+      <c r="C47" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="12" t="s">
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="34" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="39" t="s">
+      <c r="C48" s="11">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="13">
-        <v>4250000</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="41">
+      <c r="C49" s="36">
         <v>1850000</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="15">
+      <c r="B50" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="13">
         <f>SUM(C48:C49)</f>
         <v>6100000</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="53" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="11"/>
+      <c r="B53" s="9"/>
     </row>
     <row r="54" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="D54" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="42" t="s">
+      <c r="E54" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="42" t="s">
+      <c r="F54" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="42" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="43">
+      <c r="B55" s="38">
         <v>46239</v>
       </c>
-      <c r="C55" s="44">
+      <c r="C55" s="39">
         <v>850000</v>
       </c>
-      <c r="D55" s="44">
+      <c r="D55" s="39">
         <v>720000</v>
       </c>
-      <c r="E55" s="45">
+      <c r="E55" s="40">
         <f>IF(C55&gt;0, D55/C55, 0)</f>
         <v>0.84705882352941175</v>
       </c>
-      <c r="F55" s="44">
+      <c r="F55" s="39">
         <v>500000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B43:C43"/>
+  <mergeCells count="2">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="6">

--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515F548B-43F7-4C5F-9BEC-AB4E3E040E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C6F29-0210-4932-BA31-D9E92E2AB1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
   <si>
     <t>اسم المشروع</t>
   </si>
@@ -45,9 +45,6 @@
     <t>إيرادات أخري</t>
   </si>
   <si>
-    <t>الإجمالي</t>
-  </si>
-  <si>
     <t>النوع</t>
   </si>
   <si>
@@ -123,36 +120,18 @@
     <t>المتبقي للقرض</t>
   </si>
   <si>
-    <t>نسبة السداد %</t>
-  </si>
-  <si>
-    <t>حالة القرض</t>
-  </si>
-  <si>
     <t>26200</t>
   </si>
   <si>
-    <t>تم السداد بالكامل</t>
-  </si>
-  <si>
     <t>26100</t>
   </si>
   <si>
-    <t>جاري السداد</t>
-  </si>
-  <si>
     <t>26300</t>
   </si>
   <si>
-    <t>غير مدفوع</t>
-  </si>
-  <si>
     <t>26400</t>
   </si>
   <si>
-    <t>إجمالي التسهيلات (Total Loans)</t>
-  </si>
-  <si>
     <t>بيان الدفعة</t>
   </si>
   <si>
@@ -174,18 +153,12 @@
     <t>التراكمي المدفوع</t>
   </si>
   <si>
-    <t>حالة القسط</t>
-  </si>
-  <si>
     <t>2026-05-23</t>
   </si>
   <si>
     <t>2026-07-26</t>
   </si>
   <si>
-    <t>سداد جزئي (متبقي 4.46M)</t>
-  </si>
-  <si>
     <t>2027-04-01</t>
   </si>
   <si>
@@ -201,9 +174,6 @@
     <t>2026-08-02</t>
   </si>
   <si>
-    <t>تم السداد</t>
-  </si>
-  <si>
     <t>2027-02-02</t>
   </si>
   <si>
@@ -217,9 +187,6 @@
   </si>
   <si>
     <t>2029-02-02</t>
-  </si>
-  <si>
-    <t>إجمالي الأقساط والدفعات (Total Installments)</t>
   </si>
   <si>
     <t>نوع الايراد</t>
@@ -286,7 +253,7 @@
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,15 +281,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,12 +293,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9EEF4"/>
-        <bgColor rgb="FFE9EEF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -354,7 +308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -374,17 +328,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -529,30 +472,20 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -560,96 +493,72 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="52">
     <dxf>
       <font>
         <b val="0"/>
@@ -674,75 +583,6 @@
           <color rgb="FFD9D9D9"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
         <top style="thin">
           <color rgb="FFD9D9D9"/>
         </top>
@@ -1798,39 +1638,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2161,76 +1968,71 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:J7" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
-  <autoFilter ref="B3:J7" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}"/>
-  <tableColumns count="9">
-    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:H7" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="B3:H7" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}"/>
+  <tableColumns count="7">
+    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="4">
       <calculatedColumnFormula>IF(D4&gt;0, (F4-D4)/D4, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="5">
-      <calculatedColumnFormula>SUMIF($B$12:$B$23, B4, $F$12:$F$23)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="3">
+      <calculatedColumnFormula>SUMIF($B$11:$B$22, B4, $F$11:$F$22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="4">
-      <calculatedColumnFormula>SUMIF($B$12:$B$23, B4, $G$12:$G$23)</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="2">
+      <calculatedColumnFormula>SUMIF($B$11:$B$22, B4, $G$11:$G$22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="1">
       <calculatedColumnFormula>F4-G4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1078F62B-3C12-467A-8037-C551AFC45BAE}" name="نسبة السداد %" dataDxfId="2">
-      <calculatedColumnFormula>IF(F4&gt;0, G4/F4, 0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{8CB32CEA-EA37-4F1D-9E25-9783A00F1897}" name="حالة القرض" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B11:J23" totalsRowShown="0" headerRowDxfId="41" dataDxfId="42" headerRowBorderDxfId="53" tableBorderDxfId="54" totalsRowBorderDxfId="52">
-  <autoFilter ref="B11:J23" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}"/>
-  <tableColumns count="9">
-    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="48">
-      <calculatedColumnFormula>IF(H12&gt;0,D12-TODAY(),"")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B10:I22" totalsRowShown="0" headerRowDxfId="39" dataDxfId="40" headerRowBorderDxfId="50" tableBorderDxfId="51" totalsRowBorderDxfId="49">
+  <autoFilter ref="B10:I22" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}"/>
+  <tableColumns count="8">
+    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="45">
+      <calculatedColumnFormula>IF(H11&gt;0,D11-TODAY(),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="45">
-      <calculatedColumnFormula>F12-G12</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="42">
+      <calculatedColumnFormula>F11-G11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="44">
-      <calculatedColumnFormula>I11+G12</calculatedColumnFormula>
+    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="41">
+      <calculatedColumnFormula>I10+G11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A08612B9-95BC-4628-A43C-26F0A8B3B756}" name="حالة القسط" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B30:C35" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
-  <autoFilter ref="B30:C35" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B28:C32" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+  <autoFilter ref="B28:C32" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}"/>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B38:F43" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
-  <autoFilter ref="B38:F43" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B35:F39" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="31" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+  <autoFilter ref="B35:F39" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="26"/>
     <tableColumn id="6" xr3:uid="{7BB8F3DA-2FCB-4C6E-979A-002269AD8AD1}" name="إجمالي التكلفة" dataDxfId="0">
       <calculatedColumnFormula>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</calculatedColumnFormula>
     </tableColumn>
@@ -2240,27 +2042,27 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B47:C49" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="26">
-  <autoFilter ref="B47:C49" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B43:C45" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="24">
+  <autoFilter ref="B43:C45" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B54:F55" totalsRowShown="0" headerRowDxfId="15" dataDxfId="16" tableBorderDxfId="22">
-  <autoFilter ref="B54:F55" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B49:F50" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14" tableBorderDxfId="20">
+  <autoFilter ref="B49:F50" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="18">
-      <calculatedColumnFormula>IF(C55&gt;0, D55/C55, 0)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="16">
+      <calculatedColumnFormula>IF(C50&gt;0, D50/C50, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2551,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBA6161-56C5-4337-93A2-261B2C24E42D}">
-  <dimension ref="B2:K55"/>
+  <dimension ref="B2:K50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
@@ -2566,914 +2368,743 @@
   <sheetData>
     <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="14">
+        <v>56</v>
+      </c>
+      <c r="D4" s="10">
         <v>2600000</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <f>IF(D4&gt;0, (F4-D4)/D4, 0)</f>
         <v>0.14560000000000001</v>
       </c>
-      <c r="F4" s="14">
-        <f>SUMIF($B$12:$B$23, B4, $F$12:$F$23)</f>
+      <c r="F4" s="10">
+        <f>SUMIF($B$11:$B$22, B4, $F$11:$F$22)</f>
         <v>2978560</v>
       </c>
-      <c r="G4" s="14">
-        <f>SUMIF($B$12:$B$23, B4, $G$12:$G$23)</f>
+      <c r="G4" s="10">
+        <f>SUMIF($B$11:$B$22, B4, $G$11:$G$22)</f>
         <v>2978560</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="10">
         <f>F4-G4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="15">
-        <f>IF(F4&gt;0, G4/F4, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="14">
+        <v>57</v>
+      </c>
+      <c r="D5" s="10">
         <v>4400000</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <f>IF(D5&gt;0, (F5-D5)/D5, 0)</f>
         <v>0.18293000000000001</v>
       </c>
-      <c r="F5" s="14">
-        <f>SUMIF($B$12:$B$23, B5, $F$12:$F$23)</f>
+      <c r="F5" s="10">
+        <f>SUMIF($B$11:$B$22, B5, $F$11:$F$22)</f>
         <v>5204892</v>
       </c>
-      <c r="G5" s="14">
-        <f>SUMIF($B$12:$B$23, B5, $G$12:$G$23)</f>
+      <c r="G5" s="10">
+        <f>SUMIF($B$11:$B$22, B5, $G$11:$G$22)</f>
         <v>740440</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <f>F5-G5</f>
         <v>4464452</v>
       </c>
-      <c r="I5" s="15">
-        <f>IF(F5&gt;0, G5/F5, 0)</f>
-        <v>0.14225847529593313</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="14">
+        <v>58</v>
+      </c>
+      <c r="D6" s="10">
         <v>3500000</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <f>IF(D6&gt;0, (F6-D6)/D6, 0)</f>
         <v>0.21060000000000001</v>
       </c>
-      <c r="F6" s="14">
-        <f>SUMIF($B$12:$B$23, B6, $F$12:$F$23)</f>
+      <c r="F6" s="10">
+        <f>SUMIF($B$11:$B$22, B6, $F$11:$F$22)</f>
         <v>4237100</v>
       </c>
-      <c r="G6" s="14">
-        <f>SUMIF($B$12:$B$23, B6, $G$12:$G$23)</f>
+      <c r="G6" s="10">
+        <f>SUMIF($B$11:$B$22, B6, $G$11:$G$22)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <f>F6-G6</f>
         <v>4237100</v>
       </c>
-      <c r="I6" s="15">
-        <f>IF(F6&gt;0, G6/F6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="23">
+      <c r="B7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="17">
         <v>2200000</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <f>IF(D7&gt;0, (F7-D7)/D7, 0)</f>
         <v>0.315</v>
       </c>
-      <c r="F7" s="23">
-        <f>SUMIF($B$12:$B$23, B7, $F$12:$F$23)</f>
+      <c r="F7" s="17">
+        <f>SUMIF($B$11:$B$22, B7, $F$11:$F$22)</f>
         <v>2893000</v>
       </c>
-      <c r="G7" s="23">
-        <f>SUMIF($B$12:$B$23, B7, $G$12:$G$23)</f>
+      <c r="G7" s="17">
+        <f>SUMIF($B$11:$B$22, B7, $G$11:$G$22)</f>
         <v>115500</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="17">
         <f>F7-G7</f>
         <v>2777500</v>
       </c>
-      <c r="I7" s="24">
-        <f>IF(F7&gt;0, G7/F7, 0)</f>
-        <v>3.9923954372623575E-2</v>
-      </c>
-      <c r="J7" s="28" t="s">
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+    </row>
+    <row r="10" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="5" t="s">
+      <c r="F10" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="16">
-        <f>SUM(D4:D7)</f>
-        <v>12700000</v>
-      </c>
-      <c r="E8" s="17">
-        <f>IF(D8&gt;0, (F8-D8)/D8, 0)</f>
-        <v>0.20579149606299213</v>
-      </c>
-      <c r="F8" s="16">
-        <f>SUM(F4:F7)</f>
-        <v>15313552</v>
-      </c>
-      <c r="G8" s="16">
-        <f>SUM(G4:G7)</f>
-        <v>3834500</v>
-      </c>
-      <c r="H8" s="16">
-        <f>SUM(H4:H7)</f>
-        <v>11479052</v>
-      </c>
-      <c r="I8" s="17">
-        <f>IF(F8&gt;0, G8/F8, 0)</f>
-        <v>0.25039912359980232</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="26" t="s">
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="27" t="s">
-        <v>49</v>
+      <c r="E11" s="14" t="str">
+        <f ca="1">IF(H11&gt;0,D11-TODAY(),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="10">
+        <v>2978560</v>
+      </c>
+      <c r="G11" s="10">
+        <v>2978560</v>
+      </c>
+      <c r="H11" s="10">
+        <f>F11-G11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <f>G11</f>
+        <v>2978560</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="20" t="str">
+        <v>43</v>
+      </c>
+      <c r="E12" s="14">
         <f ca="1">IF(H12&gt;0,D12-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="14">
-        <v>2978560</v>
-      </c>
-      <c r="G12" s="14">
-        <v>2978560</v>
-      </c>
-      <c r="H12" s="14">
+        <v>-23</v>
+      </c>
+      <c r="F12" s="10">
+        <v>5204892</v>
+      </c>
+      <c r="G12" s="10">
+        <v>740440</v>
+      </c>
+      <c r="H12" s="10">
         <f>F12-G12</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="14">
-        <f>G12</f>
-        <v>2978560</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>35</v>
+        <v>4464452</v>
+      </c>
+      <c r="I12" s="10">
+        <f>I11+G12</f>
+        <v>3719000</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="20">
+        <v>44</v>
+      </c>
+      <c r="E13" s="14">
         <f ca="1">IF(H13&gt;0,D13-TODAY(),"")</f>
-        <v>-23</v>
-      </c>
-      <c r="F13" s="14">
-        <v>5204892</v>
-      </c>
-      <c r="G13" s="14">
-        <v>740440</v>
-      </c>
-      <c r="H13" s="14">
+        <v>226</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1210600</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
         <f>F13-G13</f>
-        <v>4464452</v>
-      </c>
-      <c r="I13" s="14">
+        <v>1210600</v>
+      </c>
+      <c r="I13" s="10">
         <f>I12+G13</f>
         <v>3719000</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="20">
+        <v>45</v>
+      </c>
+      <c r="E14" s="14">
         <f ca="1">IF(H14&gt;0,D14-TODAY(),"")</f>
-        <v>226</v>
-      </c>
-      <c r="F14" s="14">
+        <v>239</v>
+      </c>
+      <c r="F14" s="10">
         <v>1210600</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="10">
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="10">
         <f>F14-G14</f>
         <v>1210600</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="10">
         <f>I13+G14</f>
         <v>3719000</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="20">
+        <v>46</v>
+      </c>
+      <c r="E15" s="14">
         <f ca="1">IF(H15&gt;0,D15-TODAY(),"")</f>
-        <v>239</v>
-      </c>
-      <c r="F15" s="14">
+        <v>266</v>
+      </c>
+      <c r="F15" s="10">
         <v>1210600</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="10">
         <v>0</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="10">
         <f>F15-G15</f>
         <v>1210600</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="10">
         <f>I14+G15</f>
         <v>3719000</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="20">
+        <v>47</v>
+      </c>
+      <c r="E16" s="14">
         <f ca="1">IF(H16&gt;0,D16-TODAY(),"")</f>
-        <v>266</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1210600</v>
-      </c>
-      <c r="G16" s="14">
+        <v>287</v>
+      </c>
+      <c r="F16" s="10">
+        <v>605300</v>
+      </c>
+      <c r="G16" s="10">
         <v>0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="10">
         <f>F16-G16</f>
-        <v>1210600</v>
-      </c>
-      <c r="I16" s="14">
+        <v>605300</v>
+      </c>
+      <c r="I16" s="10">
         <f>I15+G16</f>
         <v>3719000</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="20">
+        <v>48</v>
+      </c>
+      <c r="E17" s="14" t="str">
         <f ca="1">IF(H17&gt;0,D17-TODAY(),"")</f>
-        <v>287</v>
-      </c>
-      <c r="F17" s="14">
-        <v>605300</v>
-      </c>
-      <c r="G17" s="14">
+        <v/>
+      </c>
+      <c r="F17" s="10">
+        <v>115500</v>
+      </c>
+      <c r="G17" s="10">
+        <v>115500</v>
+      </c>
+      <c r="H17" s="10">
+        <f>F17-G17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="14">
-        <f>F17-G17</f>
-        <v>605300</v>
-      </c>
-      <c r="I17" s="14">
+      <c r="I17" s="10">
         <f>I16+G17</f>
-        <v>3719000</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+        <v>3834500</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="20" t="str">
+        <v>49</v>
+      </c>
+      <c r="E18" s="14">
         <f ca="1">IF(H18&gt;0,D18-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="14">
+        <v>168</v>
+      </c>
+      <c r="F18" s="10">
         <v>115500</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="10">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10">
+        <f>F18-G18</f>
         <v>115500</v>
       </c>
-      <c r="H18" s="14">
-        <f>F18-G18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="14">
+      <c r="I18" s="10">
         <f>I17+G18</f>
         <v>3834500</v>
       </c>
-      <c r="J18" s="25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="20">
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
         <f ca="1">IF(H19&gt;0,D19-TODAY(),"")</f>
-        <v>168</v>
-      </c>
-      <c r="F19" s="14">
+        <v>349</v>
+      </c>
+      <c r="F19" s="10">
         <v>115500</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="10">
         <v>0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="10">
         <f>F19-G19</f>
         <v>115500</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="10">
         <f>I18+G19</f>
         <v>3834500</v>
       </c>
-      <c r="J19" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="20">
+        <v>51</v>
+      </c>
+      <c r="E20" s="14">
         <f ca="1">IF(H20&gt;0,D20-TODAY(),"")</f>
-        <v>349</v>
-      </c>
-      <c r="F20" s="14">
+        <v>533</v>
+      </c>
+      <c r="F20" s="10">
         <v>115500</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="10">
         <v>0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="10">
         <f>F20-G20</f>
         <v>115500</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="10">
         <f>I19+G20</f>
         <v>3834500</v>
       </c>
-      <c r="J20" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="20">
+        <v>52</v>
+      </c>
+      <c r="E21" s="14">
         <f ca="1">IF(H21&gt;0,D21-TODAY(),"")</f>
-        <v>533</v>
-      </c>
-      <c r="F21" s="14">
+        <v>715</v>
+      </c>
+      <c r="F21" s="10">
         <v>115500</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="10">
         <v>0</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="10">
         <f>F21-G21</f>
         <v>115500</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="10">
         <f>I20+G21</f>
         <v>3834500</v>
       </c>
-      <c r="J21" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
-        <v>40</v>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="20">
+        <v>71</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="21">
         <f ca="1">IF(H22&gt;0,D22-TODAY(),"")</f>
-        <v>715</v>
-      </c>
-      <c r="F22" s="14">
-        <v>115500</v>
-      </c>
-      <c r="G22" s="14">
+        <v>899</v>
+      </c>
+      <c r="F22" s="17">
+        <v>2315500</v>
+      </c>
+      <c r="G22" s="17">
         <v>0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="17">
         <f>F22-G22</f>
-        <v>115500</v>
-      </c>
-      <c r="I22" s="14">
+        <v>2315500</v>
+      </c>
+      <c r="I22" s="17">
         <f>I21+G22</f>
         <v>3834500</v>
       </c>
-      <c r="J22" s="25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="29">
-        <f ca="1">IF(H23&gt;0,D23-TODAY(),"")</f>
-        <v>899</v>
-      </c>
-      <c r="F23" s="23">
-        <v>2315500</v>
-      </c>
-      <c r="G23" s="23">
+    </row>
+    <row r="27" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="22">
+        <v>1810000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="22">
+        <v>1925000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="22">
+        <v>4070000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="23">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H23" s="23">
-        <f>F23-G23</f>
-        <v>2315500</v>
-      </c>
-      <c r="I23" s="23">
-        <f>I22+G23</f>
-        <v>3834500</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="16">
-        <f>SUM(F12:F23)</f>
-        <v>15313552</v>
-      </c>
-      <c r="G24" s="16">
-        <f>SUM(G12:G23)</f>
-        <v>3834500</v>
-      </c>
-      <c r="H24" s="16">
-        <f>SUM(H12:H23)</f>
-        <v>11479052</v>
-      </c>
-      <c r="I24" s="16">
-        <f>I23</f>
-        <v>3834500</v>
-      </c>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="30">
-        <v>1810000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="30">
-        <v>1925000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="30">
-        <v>4070000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="31">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="42" t="s">
+      <c r="C35" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="43">
-        <f>SUBTOTAL(109,C31:C34)</f>
-        <v>7855000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="D35" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="26" t="s">
+      <c r="F35" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="27" t="s">
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="D36" s="4">
         <v>5000000</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E36" s="4">
         <v>13000000</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F36" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
         <v>18000000</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="3" t="s">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="4">
+      <c r="C37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="4">
         <v>3500000</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E37" s="4">
         <v>8000000</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F37" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
         <v>11500000</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="4">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="4">
         <v>8000000</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E38" s="4">
         <v>27000000</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F38" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
         <v>35000000</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="22" t="s">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="32">
+      <c r="D39" s="24">
         <v>4200000</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E39" s="24">
         <v>6800000</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F39" s="23">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
         <v>11000000</v>
       </c>
     </row>
+    <row r="42" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+    </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="42"/>
-      <c r="D43" s="44">
-        <f>SUBTOTAL(109,D39:D42)</f>
-        <v>20700000</v>
-      </c>
-      <c r="E43" s="44">
-        <f>SUBTOTAL(109,E39:E42)</f>
-        <v>54800000</v>
-      </c>
-      <c r="F43" s="43">
-        <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>75500000</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="33" t="s">
+      <c r="B43" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="10" t="s">
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="26" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="34" t="s">
+      <c r="C44" s="9">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="11">
-        <v>4250000</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="35" t="s">
+      <c r="C45" s="28">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B48" s="7"/>
+    </row>
+    <row r="49" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="36">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="13">
-        <f>SUM(C48:C49)</f>
-        <v>6100000</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="53" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="9"/>
-    </row>
-    <row r="54" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B54" s="37" t="s">
+      <c r="C49" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="D49" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="E49" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="F49" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="F54" s="37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="38">
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="30">
         <v>46239</v>
       </c>
-      <c r="C55" s="39">
+      <c r="C50" s="31">
         <v>850000</v>
       </c>
-      <c r="D55" s="39">
+      <c r="D50" s="31">
         <v>720000</v>
       </c>
-      <c r="E55" s="40">
-        <f>IF(C55&gt;0, D55/C55, 0)</f>
+      <c r="E50" s="32">
+        <f>IF(C50&gt;0, D50/C50, 0)</f>
         <v>0.84705882352941175</v>
       </c>
-      <c r="F55" s="39">
+      <c r="F50" s="31">
         <v>500000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B24:C24"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="6">
     <tablePart r:id="rId1"/>

--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C6F29-0210-4932-BA31-D9E92E2AB1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ADAD6C-A5C8-4237-B850-BCC8C4C16599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>اسم المشروع</t>
   </si>
@@ -54,24 +54,9 @@
     <t>إجمالي التكلفة</t>
   </si>
   <si>
-    <t>مشروع أبراج النرجس (تطوير)</t>
-  </si>
-  <si>
     <t>رواز</t>
   </si>
   <si>
-    <t>مشروع فيلا المرسلات (تطوير)</t>
-  </si>
-  <si>
-    <t>مشروع مجمع العارض (تطوير)</t>
-  </si>
-  <si>
-    <t>مشروع أرض الملقا (تطوير سكني)</t>
-  </si>
-  <si>
-    <t>مقاولات</t>
-  </si>
-  <si>
     <t>البنك</t>
   </si>
   <si>
@@ -241,19 +226,49 @@
   </si>
   <si>
     <t>أملاك (2.2M دفعة 6)</t>
+  </si>
+  <si>
+    <t>الشريك</t>
+  </si>
+  <si>
+    <t>باسم الشمري</t>
+  </si>
+  <si>
+    <t>احمد زيدان</t>
+  </si>
+  <si>
+    <t>رواز 1 الرمال</t>
+  </si>
+  <si>
+    <t>رواز 2 العليا</t>
+  </si>
+  <si>
+    <t>رواز 3 العليا</t>
+  </si>
+  <si>
+    <t>رواز 4 العليا</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,7 +297,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +320,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor rgb="FF203764"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -455,110 +476,277 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -980,159 +1168,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1968,22 +2003,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:H7" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}" name="القروض" displayName="القروض" ref="B3:H7" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
   <autoFilter ref="B3:H7" xr:uid="{08CD83D5-1931-4B35-8A99-E4A407F4EBFD}"/>
   <tableColumns count="7">
-    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="4">
+    <tableColumn id="2" xr3:uid="{5E3D9E1A-9B3C-4A23-83F2-0DB3EC1E60AA}" name="كود الحساب (GL)" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{F7436720-8196-408A-B866-316D468EA7BC}" name="جهة التمويل" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{F84D90CB-D651-430B-9356-0F342EBEC0BF}" name="أصل التمويل" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{48627032-5E4A-4A56-A81D-2C79392F5CE8}" name="الفائدة %" dataDxfId="11">
       <calculatedColumnFormula>IF(D4&gt;0, (F4-D4)/D4, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{A8D25AC8-67C6-4470-BD22-1EAE8530E3BB}" name="المبلغ المستحق" dataDxfId="10">
       <calculatedColumnFormula>SUMIF($B$11:$B$22, B4, $F$11:$F$22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{3DF05E27-6A99-43C9-B538-D1D6C8982C87}" name="إجمالي المدفوع" dataDxfId="9">
       <calculatedColumnFormula>SUMIF($B$11:$B$22, B4, $G$11:$G$22)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{4EA4398A-E6E8-447C-B4E3-DEAA1A0E6734}" name="المتبقي للقرض" dataDxfId="8">
       <calculatedColumnFormula>F4-G4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1992,21 +2027,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B10:I22" totalsRowShown="0" headerRowDxfId="39" dataDxfId="40" headerRowBorderDxfId="50" tableBorderDxfId="51" totalsRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}" name="الاقساط" displayName="الاقساط" ref="B10:I22" totalsRowShown="0" headerRowDxfId="41" dataDxfId="42" headerRowBorderDxfId="52" tableBorderDxfId="53" totalsRowBorderDxfId="51">
   <autoFilter ref="B10:I22" xr:uid="{25AAF0B2-D36A-4622-800D-72805C479F28}"/>
   <tableColumns count="8">
-    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="45">
+    <tableColumn id="2" xr3:uid="{7BB86E06-1A48-467C-839F-816330EF31B1}" name="كود الحساب (GL)" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{E61F7A2D-BDC4-44F2-9335-E08D00CEB732}" name="بيان الدفعة" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{56A6BA54-5C3E-4F92-A23D-18D91501502E}" name="تاريخ الاستحقاق" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{87BB5917-20F9-4D3C-9041-43B648390544}" name="الأيام المتبقية" dataDxfId="47">
       <calculatedColumnFormula>IF(H11&gt;0,D11-TODAY(),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="42">
+    <tableColumn id="6" xr3:uid="{4BF6EAC8-5A7A-47D3-B2A5-5F582211D62A}" name="المستحق للدفعة" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{CC67325F-FE21-49C6-9292-73A1138CD826}" name="المبلغ المدفوع" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{6D77BBC6-6E9B-42E6-9FF1-962456ABA0CB}" name="المتبقي للدفعة" dataDxfId="44">
       <calculatedColumnFormula>F11-G11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="41">
+    <tableColumn id="9" xr3:uid="{E4074BF7-E861-42DB-BA5A-CAC946F0F451}" name="التراكمي المدفوع" dataDxfId="43">
       <calculatedColumnFormula>I10+G11</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2015,25 +2050,25 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B28:C32" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}" name="الايردات" displayName="الايردات" ref="B28:C32" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
   <autoFilter ref="B28:C32" xr:uid="{84807BD5-3D87-41B5-AE11-59954A1C6826}"/>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{87AD5B20-FF69-4AD5-B4B6-23C3CAC7F211}" name="نوع الايراد" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{0ADCFFAE-62DD-4A08-9DF2-B64FEA5527E7}" name="المبلغ" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B35:F39" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="31" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}" name="Units_Under_Construction" displayName="Units_Under_Construction" ref="B35:F39" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
   <autoFilter ref="B35:F39" xr:uid="{D62D120E-3DD5-4187-A81E-67C0C0ABB71C}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{7BB8F3DA-2FCB-4C6E-979A-002269AD8AD1}" name="إجمالي التكلفة" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{37E43D9A-02AD-42E3-A43D-2358F2E18C8D}" name="اسم المشروع" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{80318650-E498-42B7-98C4-E5D2FFCBF0D1}" name="النوع" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{80AA303F-C631-41B6-BA7B-33FB06AB9942}" name="قيمة الأرض" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{8668B584-08A1-44F1-BA20-8DE2619AD7E6}" name="قيمة التطوير" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{7BB8F3DA-2FCB-4C6E-979A-002269AD8AD1}" name="إجمالي التكلفة" dataDxfId="7">
       <calculatedColumnFormula>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2042,27 +2077,38 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B43:C45" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}" name="البنوك" displayName="البنوك" ref="B43:C45" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="26">
   <autoFilter ref="B43:C45" xr:uid="{BB2630AF-E8DA-4685-A56F-4C2FCBF08954}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{AAA88640-6019-4F48-A9C2-AC06E77B0248}" name="البنك" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{522AD8EB-0CDA-40D1-8C62-09844870006E}" name="الرصيد" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B49:F50" totalsRowShown="0" headerRowDxfId="13" dataDxfId="14" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}" name="تحصيلات_الايجار" displayName="تحصيلات_الايجار" ref="B49:F50" totalsRowShown="0" headerRowDxfId="20" dataDxfId="21" tableBorderDxfId="22">
   <autoFilter ref="B49:F50" xr:uid="{047962E8-D4E2-49BC-B4CA-5F7601A52109}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{FBE8A87F-F4FF-430D-BB6E-9842BDA03389}" name="الشهر" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{80069C6C-993B-46EA-8CEE-B6E352F9CB27}" name="المستحق للتحصيل" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F7BC38F8-3F20-44EC-B882-B42317D364D5}" name="المحصل الفعلي" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{CD71EAF6-9941-4277-BF01-4C630D923114}" name="كفاءة التحصيل %" dataDxfId="1">
       <calculatedColumnFormula>IF(C50&gt;0, D50/C50, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{C1C03E1E-D9BC-4EF4-A34C-34F220E83E73}" name="تحصيل الشهر القادم" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D126F323-7AC1-414B-B43D-F043C051FE5B}" name="حساب_الشركاء" displayName="حساب_الشركاء" ref="E28:F30" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="E28:F30" xr:uid="{D126F323-7AC1-414B-B43D-F043C051FE5B}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{BA8AFAF7-6F35-4757-952D-E998AD20B322}" name="الشريك"/>
+    <tableColumn id="2" xr3:uid="{7E82D2A6-AF8C-406E-A64D-8D5E51612725}" name="الرصيد" dataDxfId="6" dataCellStyle="Comma"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2380,33 +2426,33 @@
     </row>
     <row r="3" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D4" s="10">
         <v>2600000</v>
@@ -2430,10 +2476,10 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D5" s="10">
         <v>4400000</v>
@@ -2457,10 +2503,10 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D6" s="10">
         <v>3500000</v>
@@ -2484,10 +2530,10 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D7" s="17">
         <v>2200000</v>
@@ -2526,39 +2572,39 @@
     </row>
     <row r="10" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="19" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="I10" s="19" t="s">
         <v>36</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E11" s="14" t="str">
         <f ca="1">IF(H11&gt;0,D11-TODAY(),"")</f>
@@ -2581,13 +2627,13 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E12" s="14">
         <f ca="1">IF(H12&gt;0,D12-TODAY(),"")</f>
@@ -2610,13 +2656,13 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E13" s="14">
         <f ca="1">IF(H13&gt;0,D13-TODAY(),"")</f>
@@ -2639,13 +2685,13 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E14" s="14">
         <f ca="1">IF(H14&gt;0,D14-TODAY(),"")</f>
@@ -2668,13 +2714,13 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" s="14">
         <f ca="1">IF(H15&gt;0,D15-TODAY(),"")</f>
@@ -2697,13 +2743,13 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E16" s="14">
         <f ca="1">IF(H16&gt;0,D16-TODAY(),"")</f>
@@ -2726,13 +2772,13 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E17" s="14" t="str">
         <f ca="1">IF(H17&gt;0,D17-TODAY(),"")</f>
@@ -2755,13 +2801,13 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E18" s="14">
         <f ca="1">IF(H18&gt;0,D18-TODAY(),"")</f>
@@ -2784,13 +2830,13 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E19" s="14">
         <f ca="1">IF(H19&gt;0,D19-TODAY(),"")</f>
@@ -2813,13 +2859,13 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E20" s="14">
         <f ca="1">IF(H20&gt;0,D20-TODAY(),"")</f>
@@ -2842,13 +2888,13 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E21" s="14">
         <f ca="1">IF(H21&gt;0,D21-TODAY(),"")</f>
@@ -2871,13 +2917,13 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E22" s="21">
         <f ca="1">IF(H22&gt;0,D22-TODAY(),"")</f>
@@ -2903,10 +2949,16 @@
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
@@ -2916,6 +2968,12 @@
       <c r="C29" s="22">
         <v>1810000</v>
       </c>
+      <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="32">
+        <v>-56863.839150000247</v>
+      </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
@@ -2923,6 +2981,12 @@
       </c>
       <c r="C30" s="22">
         <v>1925000</v>
+      </c>
+      <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="32">
+        <v>400000</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
@@ -2968,75 +3032,82 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="D36" s="4">
-        <v>5000000</v>
+        <v>2247500</v>
       </c>
       <c r="E36" s="4">
-        <v>13000000</v>
+        <v>1613573.620000001</v>
       </c>
       <c r="F36" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>18000000</v>
+        <v>3861073.620000001</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="4">
-        <v>3500000</v>
+        <v>4700000</v>
       </c>
       <c r="E37" s="4">
-        <v>8000000</v>
+        <v>2447405.6700000064</v>
       </c>
       <c r="F37" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>11500000</v>
+        <v>7147405.6700000064</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="4">
-        <v>8000000</v>
+        <v>4000000</v>
       </c>
       <c r="E38" s="4">
-        <v>27000000</v>
+        <v>1841514.4599999962</v>
       </c>
       <c r="F38" s="22">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>35000000</v>
+        <v>5841514.4599999962</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>14</v>
+        <v>73</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D39" s="24">
-        <v>4200000</v>
+        <v>4427280</v>
       </c>
       <c r="E39" s="24">
-        <v>6800000</v>
+        <v>683670.41999999993</v>
       </c>
       <c r="F39" s="23">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>11000000</v>
-      </c>
+        <v>5110950.42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
     </row>
     <row r="42" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
@@ -3044,75 +3115,76 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="25" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C44" s="9">
-        <v>4250000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C45" s="28">
-        <v>1850000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
     </row>
-    <row r="49" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="29" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="30">
         <v>46239</v>
       </c>
-      <c r="C50" s="31">
-        <v>850000</v>
-      </c>
-      <c r="D50" s="31">
-        <v>720000</v>
-      </c>
-      <c r="E50" s="32">
+      <c r="C50" s="34">
+        <v>186156</v>
+      </c>
+      <c r="D50" s="34">
+        <v>13750</v>
+      </c>
+      <c r="E50" s="31">
         <f>IF(C50&gt;0, D50/C50, 0)</f>
-        <v>0.84705882352941175</v>
-      </c>
-      <c r="F50" s="31">
-        <v>500000</v>
+        <v>7.3862781752938395E-2</v>
+      </c>
+      <c r="F50" s="34">
+        <v>300115</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
+  <tableParts count="7">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ADAD6C-A5C8-4237-B850-BCC8C4C16599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB54A86-831F-45C2-A91F-157297C20485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -2980,7 +2980,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="22">
-        <v>1925000</v>
+        <v>1260000</v>
       </c>
       <c r="E30" t="s">
         <v>69</v>
@@ -2994,7 +2994,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="22">
-        <v>4070000</v>
+        <v>4848824</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
@@ -3002,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="23">
-        <v>50000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">

--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB54A86-831F-45C2-A91F-157297C20485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029B9DB6-E453-4669-BDE0-7A77C461F4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>

--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029B9DB6-E453-4669-BDE0-7A77C461F4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39617032-B68C-4699-B146-61EDA3A91AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -2972,7 +2972,7 @@
         <v>68</v>
       </c>
       <c r="F29" s="32">
-        <v>-56863.839150000247</v>
+        <v>56863.839999999997</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
@@ -2986,7 +2986,7 @@
         <v>69</v>
       </c>
       <c r="F30" s="32">
-        <v>400000</v>
+        <v>-400000</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">

--- a/Master_Financial_Data_F.xlsx
+++ b/Master_Financial_Data_F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\سدرة الخير\Hub Project Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39617032-B68C-4699-B146-61EDA3A91AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFD2AD0-895C-4DBB-A184-E5EBD087FB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A5F8E36-84B9-447B-B8EE-2145B847F993}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E12" s="14">
         <f ca="1">IF(H12&gt;0,D12-TODAY(),"")</f>
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="F12" s="10">
         <v>5204892</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E13" s="14">
         <f ca="1">IF(H13&gt;0,D13-TODAY(),"")</f>
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F13" s="10">
         <v>1210600</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E14" s="14">
         <f ca="1">IF(H14&gt;0,D14-TODAY(),"")</f>
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F14" s="10">
         <v>1210600</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E15" s="14">
         <f ca="1">IF(H15&gt;0,D15-TODAY(),"")</f>
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F15" s="10">
         <v>1210600</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="E16" s="14">
         <f ca="1">IF(H16&gt;0,D16-TODAY(),"")</f>
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F16" s="10">
         <v>605300</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E18" s="14">
         <f ca="1">IF(H18&gt;0,D18-TODAY(),"")</f>
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F18" s="10">
         <v>115500</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="E19" s="14">
         <f ca="1">IF(H19&gt;0,D19-TODAY(),"")</f>
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F19" s="10">
         <v>115500</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E20" s="14">
         <f ca="1">IF(H20&gt;0,D20-TODAY(),"")</f>
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F20" s="10">
         <v>115500</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="E21" s="14">
         <f ca="1">IF(H21&gt;0,D21-TODAY(),"")</f>
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F21" s="10">
         <v>115500</v>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E22" s="21">
         <f ca="1">IF(H22&gt;0,D22-TODAY(),"")</f>
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="F22" s="17">
         <v>2315500</v>
@@ -2972,7 +2972,7 @@
         <v>68</v>
       </c>
       <c r="F29" s="32">
-        <v>56863.839999999997</v>
+        <v>156863.84</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
@@ -3095,11 +3095,11 @@
         <v>4427280</v>
       </c>
       <c r="E39" s="24">
-        <v>683670.41999999993</v>
+        <v>783670.42</v>
       </c>
       <c r="F39" s="23">
         <f>SUM(Units_Under_Construction[[#This Row],[قيمة الأرض]:[قيمة التطوير]])</f>
-        <v>5110950.42</v>
+        <v>5210950.42</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -3126,7 +3126,7 @@
         <v>12</v>
       </c>
       <c r="C44" s="9">
-        <v>200000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -3134,7 +3134,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="28">
-        <v>20000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -3162,14 +3162,14 @@
         <v>46239</v>
       </c>
       <c r="C50" s="34">
-        <v>186156</v>
+        <v>172000</v>
       </c>
       <c r="D50" s="34">
         <v>13750</v>
       </c>
       <c r="E50" s="31">
         <f>IF(C50&gt;0, D50/C50, 0)</f>
-        <v>7.3862781752938395E-2</v>
+        <v>7.9941860465116282E-2</v>
       </c>
       <c r="F50" s="34">
         <v>300115</v>
